--- a/cet4/result/29_民国穿越_乱世佳人的逆袭人生/29_民国穿越_乱世佳人的逆袭人生_学习版.xlsx
+++ b/cet4/result/29_民国穿越_乱世佳人的逆袭人生/29_民国穿越_乱世佳人的逆袭人生_学习版.xlsx
@@ -397,871 +397,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D46"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>forty</v>
       </c>
       <c r="B2" t="str">
-        <v>forty</v>
+        <v>/ˈfɔːrti/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>四十</v>
       </c>
-      <c r="D2" t="str">
-        <v>forty(四十)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>rainy</v>
       </c>
       <c r="B3" t="str">
-        <v>rainy</v>
+        <v>/ˈreɪni/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>下雨的</v>
       </c>
-      <c r="D3" t="str">
-        <v>rainy(下雨的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>widespread</v>
       </c>
       <c r="B4" t="str">
-        <v>widespread</v>
+        <v>/ˈwaɪdspred/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>广泛的</v>
       </c>
-      <c r="D4" t="str">
-        <v>widespread(广泛的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>grandmother</v>
       </c>
       <c r="B5" t="str">
-        <v>grandmother</v>
+        <v>/ˈɡrænmʌðər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>祖母</v>
       </c>
-      <c r="D5" t="str">
-        <v>grandmother(祖母)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>elder</v>
       </c>
       <c r="B6" t="str">
-        <v>elder</v>
+        <v>/ˈeldər/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>长辈</v>
       </c>
-      <c r="D6" t="str">
-        <v>elder(长辈)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>art</v>
       </c>
       <c r="B7" t="str">
-        <v>art</v>
+        <v>/ɑːrt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>艺术</v>
       </c>
-      <c r="D7" t="str">
-        <v>art(艺术)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>distinct</v>
       </c>
       <c r="B8" t="str">
-        <v>distinct</v>
+        <v>/dɪˈstɪŋkt/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>独特的</v>
       </c>
-      <c r="D8" t="str">
-        <v>distinct(独特的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>gentleman</v>
       </c>
       <c r="B9" t="str">
-        <v>gentleman</v>
+        <v>/ˈdʒentlmən/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>绅士</v>
       </c>
-      <c r="D9" t="str">
-        <v>gentleman(绅士)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>little</v>
       </c>
       <c r="B10" t="str">
-        <v>little</v>
+        <v>/ˈlɪtl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>小的</v>
       </c>
-      <c r="D10" t="str">
-        <v>little(小的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>veteran</v>
       </c>
       <c r="B11" t="str">
-        <v>veteran</v>
+        <v>/ˈvetərən/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>老手</v>
       </c>
-      <c r="D11" t="str">
-        <v>veteran(老手)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>scientific</v>
       </c>
       <c r="B12" t="str">
-        <v>scientific</v>
+        <v>/ˌsaɪənˈtɪfɪk/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>科学的</v>
       </c>
-      <c r="D12" t="str">
-        <v>scientific(科学的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>dialog</v>
       </c>
       <c r="B13" t="str">
-        <v>dialog</v>
+        <v>/ˈdaɪəlɔːɡ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>对话</v>
       </c>
-      <c r="D13" t="str">
-        <v>dialog(对话)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>railroad</v>
       </c>
       <c r="B14" t="str">
-        <v>railroad</v>
+        <v>/ˈreɪlroʊd/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>铁路</v>
       </c>
-      <c r="D14" t="str">
-        <v>railroad(铁路)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>nation</v>
       </c>
       <c r="B15" t="str">
-        <v>nation</v>
+        <v>/ˈneɪʃn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>国家</v>
       </c>
-      <c r="D15" t="str">
-        <v>nation(国家)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>politics</v>
       </c>
       <c r="B16" t="str">
-        <v>politics</v>
+        <v>/ˈpɑːlətɪks/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>政治</v>
       </c>
-      <c r="D16" t="str">
-        <v>politics(政治)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>short</v>
       </c>
       <c r="B17" t="str">
-        <v>short</v>
+        <v>/ʃɔːrt/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>短的</v>
       </c>
-      <c r="D17" t="str">
-        <v>short(短的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>consider</v>
       </c>
       <c r="B18" t="str">
-        <v>consider</v>
+        <v>/kənˈsɪdər/</v>
       </c>
       <c r="C18" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>考虑</v>
       </c>
-      <c r="D18" t="str">
-        <v>consider(考虑)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>hand</v>
       </c>
       <c r="B19" t="str">
-        <v>hand</v>
+        <v>/hænd/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>手</v>
       </c>
-      <c r="D19" t="str">
-        <v>hand(手)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>quicken</v>
       </c>
       <c r="B20" t="str">
-        <v>art</v>
+        <v>/ˈkwɪkən/</v>
       </c>
       <c r="C20" t="str">
-        <v>艺术</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>art(艺术)📢</v>
+        <v>加快</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>fifth</v>
       </c>
       <c r="B21" t="str">
-        <v>quicken</v>
+        <v>/fɪfθ/</v>
       </c>
       <c r="C21" t="str">
-        <v>加快</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D21" t="str">
-        <v>quicken(加快)📢</v>
+        <v>第五</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>necessary</v>
       </c>
       <c r="B22" t="str">
-        <v>fifth</v>
+        <v>/ˈnesəseri/</v>
       </c>
       <c r="C22" t="str">
-        <v>第五</v>
+        <v>n./adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>fifth(第五)📢</v>
+        <v>必要的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>danger</v>
       </c>
       <c r="B23" t="str">
-        <v>politics</v>
+        <v>/ˈdeɪndʒər/</v>
       </c>
       <c r="C23" t="str">
-        <v>政治</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>politics(政治)📢</v>
+        <v>危险</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>occurrence</v>
       </c>
       <c r="B24" t="str">
-        <v>grandmother</v>
+        <v>/əˈkɜːrəns/</v>
       </c>
       <c r="C24" t="str">
-        <v>祖母</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>grandmother(祖母)📢</v>
+        <v>事件</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>serve</v>
       </c>
       <c r="B25" t="str">
-        <v>elder</v>
+        <v>/sɜːrv/</v>
       </c>
       <c r="C25" t="str">
-        <v>长辈</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>elder(长辈)📢</v>
+        <v>服务</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>dialect</v>
       </c>
       <c r="B26" t="str">
-        <v>necessary</v>
+        <v>/ˈdaɪəlekt/</v>
       </c>
       <c r="C26" t="str">
-        <v>必要的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D26" t="str">
-        <v>necessary(必要的)📢</v>
+        <v>方言</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>corn</v>
       </c>
       <c r="B27" t="str">
-        <v>danger</v>
+        <v>/kɔːrn/</v>
       </c>
       <c r="C27" t="str">
-        <v>危险</v>
+        <v>n./vt.</v>
       </c>
       <c r="D27" t="str">
-        <v>danger(危险)📢</v>
+        <v>玉米</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>real</v>
       </c>
       <c r="B28" t="str">
-        <v>occurrence</v>
+        <v>/ˈriːəl/</v>
       </c>
       <c r="C28" t="str">
-        <v>事件</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>occurrence(事件)📢</v>
+        <v>真实的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>describe</v>
       </c>
       <c r="B29" t="str">
-        <v>grandmother</v>
+        <v>/dɪˈskraɪb/</v>
       </c>
       <c r="C29" t="str">
-        <v>祖母</v>
+        <v>vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>grandmother(祖母)📢</v>
+        <v>描述</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>subsequent</v>
       </c>
       <c r="B30" t="str">
-        <v>elder</v>
+        <v>/ˈsʌbsɪkwənt/</v>
       </c>
       <c r="C30" t="str">
-        <v>长辈</v>
+        <v>adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>elder(长辈)📢</v>
+        <v>随后的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>withdraw</v>
       </c>
       <c r="B31" t="str">
-        <v>serve</v>
+        <v>/wɪðˈdrɔː/</v>
       </c>
       <c r="C31" t="str">
-        <v>服务</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>serve(服务)📢</v>
+        <v>撤退</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>discover</v>
       </c>
       <c r="B32" t="str">
-        <v>elder</v>
+        <v>/dɪˈskʌvər/</v>
       </c>
       <c r="C32" t="str">
-        <v>长辈</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>elder(长辈)📢</v>
+        <v>发现</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>energy</v>
       </c>
       <c r="B33" t="str">
-        <v>dialect</v>
+        <v>/ˈenərdʒi/</v>
       </c>
       <c r="C33" t="str">
-        <v>方言</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>dialect(方言)📢</v>
+        <v>精力</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>piece</v>
       </c>
       <c r="B34" t="str">
-        <v>grandmother</v>
+        <v>/piːs/</v>
       </c>
       <c r="C34" t="str">
-        <v>祖母</v>
+        <v>n./vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>grandmother(祖母)📢</v>
+        <v>块</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>handkerchief</v>
       </c>
       <c r="B35" t="str">
-        <v>corn</v>
+        <v>/ˈhæŋkətʃɪf/</v>
       </c>
       <c r="C35" t="str">
-        <v>玉米</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>corn(玉米)📢</v>
+        <v>手帕</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>propose</v>
       </c>
       <c r="B36" t="str">
-        <v>real</v>
+        <v>/prəˈpoʊz/</v>
       </c>
       <c r="C36" t="str">
-        <v>真实的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>real(真实的)📢</v>
+        <v>提议</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>kingdom</v>
       </c>
       <c r="B37" t="str">
-        <v>describe</v>
+        <v>/ˈkɪŋdəm/</v>
       </c>
       <c r="C37" t="str">
-        <v>描述</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>describe(描述)📢</v>
+        <v>王国</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>off</v>
       </c>
       <c r="B38" t="str">
-        <v>subsequent</v>
+        <v>/ɔːf/</v>
       </c>
       <c r="C38" t="str">
-        <v>随后的</v>
+        <v>v./adj./adv./prep.</v>
       </c>
       <c r="D38" t="str">
-        <v>subsequent(随后的)📢</v>
+        <v>离开</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>set</v>
       </c>
       <c r="B39" t="str">
-        <v>withdraw</v>
+        <v>/set/</v>
       </c>
       <c r="C39" t="str">
-        <v>撤退</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>withdraw(撤退)📢</v>
+        <v>安置</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>medical</v>
       </c>
       <c r="B40" t="str">
-        <v>discover</v>
+        <v>/ˈmedɪkl/</v>
       </c>
       <c r="C40" t="str">
-        <v>发现</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>discover(发现)📢</v>
+        <v>医学的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>conclusion</v>
       </c>
       <c r="B41" t="str">
-        <v>energy</v>
+        <v>/kənˈkluːʒn/</v>
       </c>
       <c r="C41" t="str">
-        <v>精力</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>energy(精力)📢</v>
+        <v>结论</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>fluent</v>
       </c>
       <c r="B42" t="str">
-        <v>piece</v>
+        <v>/ˈfluːənt/</v>
       </c>
       <c r="C42" t="str">
-        <v>块</v>
+        <v>adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>piece(块)📢</v>
+        <v>流利的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>generator</v>
       </c>
       <c r="B43" t="str">
-        <v>handkerchief</v>
+        <v>/ˈdʒenəreɪtər/</v>
       </c>
       <c r="C43" t="str">
-        <v>手帕</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>handkerchief(手帕)📢</v>
+        <v>发电机</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>wavelength</v>
       </c>
       <c r="B44" t="str">
-        <v>propose</v>
+        <v>/ˈweɪvleŋθ/</v>
       </c>
       <c r="C44" t="str">
-        <v>提议</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>propose(提议)📢</v>
+        <v>波长</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>together</v>
       </c>
       <c r="B45" t="str">
-        <v>grandmother</v>
+        <v>/təˈɡeðər/</v>
       </c>
       <c r="C45" t="str">
-        <v>祖母</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D45" t="str">
-        <v>grandmother(祖母)📢</v>
+        <v>一起</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>win</v>
       </c>
       <c r="B46" t="str">
-        <v>kingdom</v>
+        <v>/wɪn/</v>
       </c>
       <c r="C46" t="str">
-        <v>王国</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>kingdom(王国)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>grandmother</v>
-      </c>
-      <c r="C47" t="str">
-        <v>祖母</v>
-      </c>
-      <c r="D47" t="str">
-        <v>grandmother(祖母)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>off</v>
-      </c>
-      <c r="C48" t="str">
-        <v>离开</v>
-      </c>
-      <c r="D48" t="str">
-        <v>off(离开)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>necessary</v>
-      </c>
-      <c r="C49" t="str">
-        <v>必要的</v>
-      </c>
-      <c r="D49" t="str">
-        <v>necessary(必要的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>grandmother</v>
-      </c>
-      <c r="C50" t="str">
-        <v>祖母</v>
-      </c>
-      <c r="D50" t="str">
-        <v>grandmother(祖母)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>set</v>
-      </c>
-      <c r="C51" t="str">
-        <v>安置</v>
-      </c>
-      <c r="D51" t="str">
-        <v>set(安置)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>medical</v>
-      </c>
-      <c r="C52" t="str">
-        <v>医学的</v>
-      </c>
-      <c r="D52" t="str">
-        <v>medical(医学的)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>conclusion</v>
-      </c>
-      <c r="C53" t="str">
-        <v>结论</v>
-      </c>
-      <c r="D53" t="str">
-        <v>conclusion(结论)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>fluent</v>
-      </c>
-      <c r="C54" t="str">
-        <v>流利的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>fluent(流利的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>rainy</v>
-      </c>
-      <c r="C55" t="str">
-        <v>下雨的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>rainy(下雨的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>generator</v>
-      </c>
-      <c r="C56" t="str">
-        <v>发电机</v>
-      </c>
-      <c r="D56" t="str">
-        <v>generator(发电机)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>wavelength</v>
-      </c>
-      <c r="C57" t="str">
-        <v>波长</v>
-      </c>
-      <c r="D57" t="str">
-        <v>wavelength(波长)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>grandmother</v>
-      </c>
-      <c r="C58" t="str">
-        <v>祖母</v>
-      </c>
-      <c r="D58" t="str">
-        <v>grandmother(祖母)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>nation</v>
-      </c>
-      <c r="C59" t="str">
-        <v>国家</v>
-      </c>
-      <c r="D59" t="str">
-        <v>nation(国家)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>together</v>
-      </c>
-      <c r="C60" t="str">
-        <v>一起</v>
-      </c>
-      <c r="D60" t="str">
-        <v>together(一起)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>win</v>
-      </c>
-      <c r="C61" t="str">
         <v>赢得</v>
-      </c>
-      <c r="D61" t="str">
-        <v>win(赢得)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
   </ignoredErrors>
 </worksheet>
 </file>